--- a/排课结果/小数课重排回滚清单.xlsx
+++ b/排课结果/小数课重排回滚清单.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -722,12 +722,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>150130300.001</t>
+          <t>150013340.004</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>体育经济学</t>
+          <t>副项2</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -745,19 +745,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>150130580.006</t>
+          <t>150130300.001</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>体育经济学</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.5</v>
+        <v>1.9999999</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -768,19 +768,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>150130610.001</t>
+          <t>150130580.006</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>体育心理学</t>
+          <t>专项4</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.9999999</v>
+        <v>5.5</v>
       </c>
       <c r="D16" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -791,19 +791,19 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>150130680.005</t>
+          <t>150130610.001</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>专项2</t>
+          <t>体育心理学</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.5</v>
+        <v>1.9999999</v>
       </c>
       <c r="D17" t="n">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>150130680.006</t>
+          <t>150130680.005</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -837,19 +837,19 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>150130781.001</t>
+          <t>150130680.006</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>体育赛事组织与管理</t>
+          <t>专项2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.9999999</v>
+        <v>5.5</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -860,19 +860,19 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>150140470.004</t>
+          <t>150130781.001</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>武术竞赛与训练2</t>
+          <t>体育赛事组织与管理</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1.9999999</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -883,19 +883,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>150140670.004</t>
+          <t>150140470.004</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>专项3</t>
+          <t>武术竞赛与训练2</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3.9999998</v>
+        <v>1.9999999</v>
       </c>
       <c r="D21" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -906,19 +906,19 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>151130360.001</t>
+          <t>150140670.004</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>瑜伽</t>
+          <t>专项3</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.9999999</v>
+        <v>3.9999998</v>
       </c>
       <c r="D22" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -929,19 +929,19 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>15ALT005.001</t>
+          <t>151130360.001</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>健美操队</t>
+          <t>瑜伽</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5.5</v>
+        <v>1.9999999</v>
       </c>
       <c r="D23" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>15ALT049.001</t>
+          <t>15ALT005.001</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>足球甲组业余集训</t>
+          <t>健美操队</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="D24" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -975,19 +975,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>17716055.001</t>
+          <t>15ALT049.001</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>短视频平台运营与用户增长</t>
+          <t>足球甲组业余集训</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="D25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -998,16 +998,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>271010080.001</t>
+          <t>17716055.001</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Java EE开发技术</t>
+          <t>短视频平台运营与用户增长</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D26" t="n">
         <v>32</v>
@@ -1021,19 +1021,19 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>61051002.001</t>
+          <t>271010080.001</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>身边的管理学</t>
+          <t>Java EE开发技术</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1044,19 +1044,19 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>61051004.001</t>
+          <t>61051002.001</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>爱情心理学</t>
+          <t>身边的管理学</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.9999999</v>
+        <v>0.5</v>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1067,12 +1067,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>61451002.001</t>
+          <t>61051004.001</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>情绪管理与自我成长</t>
+          <t>爱情心理学</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1090,12 +1090,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>61660003.001</t>
+          <t>61451002.001</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>音乐美学</t>
+          <t>情绪管理与自我成长</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1113,16 +1113,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>69741001.001</t>
+          <t>61660003.001</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AIGC创意设计基础与应用</t>
+          <t>音乐美学</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.5</v>
+        <v>1.9999999</v>
       </c>
       <c r="D31" t="n">
         <v>16</v>
@@ -1136,19 +1136,19 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>69771001.001</t>
+          <t>61660013.001</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>智能制造基础技术实训</t>
+          <t>舞蹈新媒体评论</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>1.5</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1159,19 +1159,19 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>69771004.001</t>
+          <t>62251013.001</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>无人机基础与实践应用</t>
+          <t>舌尖上的危险</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1182,19 +1182,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>69771008.001</t>
+          <t>62251013.002</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>嵌入式系统开发与避障小车制作</t>
+          <t>舌尖上的危险</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1205,19 +1205,19 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>69771008.002</t>
+          <t>69741001.001</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>嵌入式系统开发与避障小车制作</t>
+          <t>AIGC创意设计基础与应用</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>0.5</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1228,21 +1228,90 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>69771004.001</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>无人机基础与实践应用</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>@A或@B无可行位，保留原ceil排法</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>69771008.001</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>嵌入式系统开发与避障小车制作</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>@A或@B无可行位，保留原ceil排法</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>69771008.002</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>嵌入式系统开发与避障小车制作</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>@A或@B无可行位，保留原ceil排法</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>69851001.002</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>心学智慧与幸福</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C39" t="n">
         <v>1.9999999</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D39" t="n">
         <v>16</v>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>@A或@B无可行位，保留原ceil排法</t>
         </is>

--- a/排课结果/小数课重排回滚清单.xlsx
+++ b/排课结果/小数课重排回滚清单.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -952,19 +952,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>15ALT005.001</t>
+          <t>17716055.001</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>健美操队</t>
+          <t>短视频平台运营与用户增长</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>5.5</v>
       </c>
       <c r="D24" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -975,19 +975,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>15ALT049.001</t>
+          <t>271010080.001</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>足球甲组业余集训</t>
+          <t>Java EE开发技术</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="D25" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -998,320 +998,21 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>17716055.001</t>
+          <t>61660003.001</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>短视频平台运营与用户增长</t>
+          <t>音乐美学</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5.5</v>
+        <v>1.9999999</v>
       </c>
       <c r="D26" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
-        <is>
-          <t>@A或@B无可行位，保留原ceil排法</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>271010080.001</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Java EE开发技术</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D27" t="n">
-        <v>32</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>@A或@B无可行位，保留原ceil排法</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>61051002.001</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>身边的管理学</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D28" t="n">
-        <v>4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>@A或@B无可行位，保留原ceil排法</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>61051004.001</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>爱情心理学</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1.9999999</v>
-      </c>
-      <c r="D29" t="n">
-        <v>16</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>@A或@B无可行位，保留原ceil排法</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>61451002.001</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>情绪管理与自我成长</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1.9999999</v>
-      </c>
-      <c r="D30" t="n">
-        <v>16</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>@A或@B无可行位，保留原ceil排法</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>61660003.001</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>音乐美学</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>1.9999999</v>
-      </c>
-      <c r="D31" t="n">
-        <v>16</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>@A或@B无可行位，保留原ceil排法</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>61660013.001</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>舞蹈新媒体评论</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D32" t="n">
-        <v>16</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>@A或@B无可行位，保留原ceil排法</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>62251013.001</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>舌尖上的危险</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D33" t="n">
-        <v>6</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>@A或@B无可行位，保留原ceil排法</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>62251013.002</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>舌尖上的危险</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D34" t="n">
-        <v>6</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>@A或@B无可行位，保留原ceil排法</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>69741001.001</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>AIGC创意设计基础与应用</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D35" t="n">
-        <v>16</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>@A或@B无可行位，保留原ceil排法</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>69771004.001</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>无人机基础与实践应用</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D36" t="n">
-        <v>4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>@A或@B无可行位，保留原ceil排法</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>69771008.001</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>嵌入式系统开发与避障小车制作</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D37" t="n">
-        <v>4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>@A或@B无可行位，保留原ceil排法</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>69771008.002</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>嵌入式系统开发与避障小车制作</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D38" t="n">
-        <v>4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>@A或@B无可行位，保留原ceil排法</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>69851001.002</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>心学智慧与幸福</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>1.9999999</v>
-      </c>
-      <c r="D39" t="n">
-        <v>16</v>
-      </c>
-      <c r="E39" t="inlineStr">
         <is>
           <t>@A或@B无可行位，保留原ceil排法</t>
         </is>
